--- a/Timesheet-Project/Timesheet 3/Jabulane/Jabulane_Poulo_March_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Jabulane/Jabulane_Poulo_March_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jabulane Poulo\Downloads\Timesheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Jabulane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{642D99BA-BB8E-4C76-AA98-8569978DD319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03822085-8123-4771-8F74-79D742A4575B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="326">
   <si>
     <t>Consultant</t>
   </si>
@@ -1036,7 +1036,7 @@
     <numFmt numFmtId="166" formatCode="_ [$R-1C09]\ * #,##0.00_ ;_ [$R-1C09]\ * \-#,##0.00_ ;_ [$R-1C09]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="[$R-1C09]#,##0.00;\-[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2119,28 +2119,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2156,6 +2141,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2214,147 +2214,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3027,6 +2886,147 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -3435,23 +3435,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H78" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H78" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
   <autoFilter ref="H2:H78" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F41" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F41" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97">
   <autoFilter ref="F2:F41" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3728,18 +3728,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -3760,7 +3760,7 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="37"/>
       <c r="B7" s="46"/>
       <c r="C7" s="37"/>
@@ -3769,7 +3769,7 @@
       <c r="H7" s="40"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>45931</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>45932</v>
       </c>
@@ -3853,7 +3853,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>45933</v>
       </c>
@@ -3872,7 +3872,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>45934</v>
       </c>
@@ -3891,7 +3891,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>45935</v>
       </c>
@@ -3910,7 +3910,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>45936</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>45937</v>
       </c>
@@ -3948,7 +3948,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>45938</v>
       </c>
@@ -3967,7 +3967,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>45939</v>
       </c>
@@ -3986,7 +3986,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>45940</v>
       </c>
@@ -4005,7 +4005,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>45941</v>
       </c>
@@ -4024,7 +4024,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>45942</v>
       </c>
@@ -4043,7 +4043,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>45943</v>
       </c>
@@ -4062,7 +4062,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>45944</v>
       </c>
@@ -4081,7 +4081,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>45945</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>45946</v>
       </c>
@@ -4119,7 +4119,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>45947</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>45948</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>45949</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>45950</v>
       </c>
@@ -4195,7 +4195,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>45951</v>
       </c>
@@ -4214,7 +4214,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>45952</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>45953</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>45954</v>
       </c>
@@ -4271,7 +4271,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>45955</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>45956</v>
       </c>
@@ -4309,7 +4309,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>45957</v>
       </c>
@@ -4328,7 +4328,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>45958</v>
       </c>
@@ -4347,7 +4347,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>45959</v>
       </c>
@@ -4366,7 +4366,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>45960</v>
       </c>
@@ -4385,7 +4385,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>45961</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
       <c r="G40" s="40"/>
@@ -4412,7 +4412,7 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="117" t="s">
         <v>27</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="118" t="s">
         <v>29</v>
       </c>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4503,7 +4503,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4514,7 +4514,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -4525,56 +4525,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
-    <cfRule type="containsText" dxfId="102" priority="12" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="95" priority="12" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="13" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="94" priority="13" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="14" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="93" priority="14" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="15" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="16" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="91" priority="16" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="17" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="90" priority="17" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="18" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B49">
-    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="4" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="5" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="6" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="8" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D41)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4622,18 +4622,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -4643,7 +4643,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -4657,10 +4657,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>45962</v>
       </c>
@@ -4711,7 +4711,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>45963</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>45964</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>45965</v>
       </c>
@@ -4782,7 +4782,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>45966</v>
       </c>
@@ -4801,7 +4801,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>45967</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>45968</v>
       </c>
@@ -4839,7 +4839,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>45969</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>45970</v>
       </c>
@@ -4877,7 +4877,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>45971</v>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>45972</v>
       </c>
@@ -4915,7 +4915,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>45973</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>45974</v>
       </c>
@@ -4953,7 +4953,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>45975</v>
       </c>
@@ -4972,7 +4972,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>45976</v>
       </c>
@@ -4991,7 +4991,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>45977</v>
       </c>
@@ -5010,7 +5010,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>45978</v>
       </c>
@@ -5029,7 +5029,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>45979</v>
       </c>
@@ -5048,7 +5048,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>45980</v>
       </c>
@@ -5067,7 +5067,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>45981</v>
       </c>
@@ -5086,7 +5086,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>45982</v>
       </c>
@@ -5105,7 +5105,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>45983</v>
       </c>
@@ -5124,7 +5124,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>45984</v>
       </c>
@@ -5143,7 +5143,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>45985</v>
       </c>
@@ -5162,7 +5162,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>45986</v>
       </c>
@@ -5181,7 +5181,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>45987</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>45988</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>45989</v>
       </c>
@@ -5238,7 +5238,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>45990</v>
       </c>
@@ -5257,7 +5257,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>45991</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="46"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -5287,7 +5287,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="117" t="s">
         <v>27</v>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9">
+    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="118" t="s">
         <v>29</v>
       </c>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1">
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5378,7 +5378,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5389,7 +5389,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1">
+    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -5400,56 +5400,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="86" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="79" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="78" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="76" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="72" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="71" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E40 D42:E44 E47">
-    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="70" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="68" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5501,18 +5501,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738C92ED-F226-4107-8C14-FCA383B998C3}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -5536,10 +5536,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>45992</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>45993</v>
       </c>
@@ -5623,7 +5623,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>45994</v>
       </c>
@@ -5642,7 +5642,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>45995</v>
       </c>
@@ -5661,7 +5661,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>45996</v>
       </c>
@@ -5680,7 +5680,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>45997</v>
       </c>
@@ -5699,7 +5699,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>45998</v>
       </c>
@@ -5718,7 +5718,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>45999</v>
       </c>
@@ -5737,7 +5737,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46000</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46001</v>
       </c>
@@ -5775,7 +5775,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46002</v>
       </c>
@@ -5794,7 +5794,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46003</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>46004</v>
       </c>
@@ -5832,7 +5832,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>46005</v>
       </c>
@@ -5851,7 +5851,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46006</v>
       </c>
@@ -5870,7 +5870,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="47">
         <v>46007</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46008</v>
       </c>
@@ -5920,7 +5920,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46009</v>
       </c>
@@ -5939,7 +5939,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46010</v>
       </c>
@@ -5958,7 +5958,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46011</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>46012</v>
       </c>
@@ -5996,7 +5996,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46013</v>
       </c>
@@ -6015,7 +6015,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46014</v>
       </c>
@@ -6034,7 +6034,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46015</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="47">
         <v>46016</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="47">
         <v>46017</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>46018</v>
       </c>
@@ -6134,7 +6134,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>46019</v>
       </c>
@@ -6153,7 +6153,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46020</v>
       </c>
@@ -6172,7 +6172,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46021</v>
       </c>
@@ -6191,7 +6191,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22">
         <v>46022</v>
       </c>
@@ -6210,7 +6210,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="45"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -6221,7 +6221,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="117" t="s">
         <v>27</v>
       </c>
@@ -6259,7 +6259,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="118" t="s">
         <v>29</v>
       </c>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6312,7 +6312,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -6323,7 +6323,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -6334,56 +6334,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="70" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="61" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="60" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="59" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="58" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="63" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6435,18 +6435,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AC14-6A48-4DDF-A891-D5BFFE7E5F3C}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -6456,7 +6456,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -6470,10 +6470,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="47">
         <v>46023</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46024</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>46025</v>
       </c>
@@ -6590,7 +6590,7 @@
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>46026</v>
       </c>
@@ -6609,7 +6609,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46027</v>
       </c>
@@ -6628,7 +6628,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46028</v>
       </c>
@@ -6647,7 +6647,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46029</v>
       </c>
@@ -6666,7 +6666,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46030</v>
       </c>
@@ -6685,7 +6685,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46031</v>
       </c>
@@ -6704,7 +6704,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>46032</v>
       </c>
@@ -6723,7 +6723,7 @@
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>46033</v>
       </c>
@@ -6742,7 +6742,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46034</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46035</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46036</v>
       </c>
@@ -6799,7 +6799,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46037</v>
       </c>
@@ -6818,7 +6818,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46038</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>46039</v>
       </c>
@@ -6856,7 +6856,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>46040</v>
       </c>
@@ -6875,7 +6875,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46041</v>
       </c>
@@ -6894,7 +6894,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46042</v>
       </c>
@@ -6913,7 +6913,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46043</v>
       </c>
@@ -6932,7 +6932,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46044</v>
       </c>
@@ -6951,7 +6951,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46045</v>
       </c>
@@ -6970,7 +6970,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>46046</v>
       </c>
@@ -6989,7 +6989,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>46047</v>
       </c>
@@ -7008,7 +7008,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46048</v>
       </c>
@@ -7027,7 +7027,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46049</v>
       </c>
@@ -7046,7 +7046,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46050</v>
       </c>
@@ -7065,7 +7065,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46051</v>
       </c>
@@ -7084,7 +7084,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46052</v>
       </c>
@@ -7103,7 +7103,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.15" thickBot="1">
+    <row r="39" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>46053</v>
       </c>
@@ -7122,7 +7122,7 @@
       <c r="I39" s="35"/>
       <c r="J39" s="35"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7133,7 +7133,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="117" t="s">
         <v>27</v>
       </c>
@@ -7171,7 +7171,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="118" t="s">
         <v>29</v>
       </c>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7224,7 +7224,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7235,7 +7235,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -7246,56 +7246,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="54" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="47" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="45" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7363,18 +7363,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5FF808-4CDC-4429-9978-CAD26FE6591A}">
   <dimension ref="A5:J46"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -7384,7 +7384,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -7398,10 +7398,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>46054</v>
       </c>
@@ -7452,7 +7452,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46055</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46056</v>
       </c>
@@ -7504,7 +7504,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46057</v>
       </c>
@@ -7523,7 +7523,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46058</v>
       </c>
@@ -7542,7 +7542,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46059</v>
       </c>
@@ -7561,7 +7561,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>46060</v>
       </c>
@@ -7580,7 +7580,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>46061</v>
       </c>
@@ -7599,7 +7599,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46062</v>
       </c>
@@ -7618,7 +7618,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46063</v>
       </c>
@@ -7637,7 +7637,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46064</v>
       </c>
@@ -7656,7 +7656,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46065</v>
       </c>
@@ -7675,7 +7675,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46066</v>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>46067</v>
       </c>
@@ -7713,7 +7713,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>46068</v>
       </c>
@@ -7732,7 +7732,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46069</v>
       </c>
@@ -7751,7 +7751,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46070</v>
       </c>
@@ -7770,7 +7770,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46071</v>
       </c>
@@ -7789,7 +7789,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46072</v>
       </c>
@@ -7808,7 +7808,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46073</v>
       </c>
@@ -7827,7 +7827,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>46074</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>46075</v>
       </c>
@@ -7865,7 +7865,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46076</v>
       </c>
@@ -7884,7 +7884,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46077</v>
       </c>
@@ -7903,7 +7903,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46078</v>
       </c>
@@ -7922,7 +7922,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46079</v>
       </c>
@@ -7941,7 +7941,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46080</v>
       </c>
@@ -7960,7 +7960,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>46081</v>
       </c>
@@ -7979,7 +7979,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="37" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="46"/>
       <c r="B37" s="45"/>
       <c r="C37" s="45"/>
@@ -7990,7 +7990,7 @@
       <c r="H37" s="36"/>
       <c r="I37" s="37"/>
     </row>
-    <row r="38" spans="1:10" ht="13.9" customHeight="1">
+    <row r="38" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H38" s="40"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="9"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H39" s="40"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="117" t="s">
         <v>27</v>
       </c>
@@ -8028,7 +8028,7 @@
       <c r="F40" s="2"/>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9">
+    <row r="41" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="6"/>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="H41" s="38"/>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="118" t="s">
         <v>29</v>
       </c>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="14.45" thickBot="1">
+    <row r="43" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9" thickBot="1">
+    <row r="44" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -8081,7 +8081,7 @@
       <c r="F44" s="2"/>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="13.9" thickBot="1">
+    <row r="45" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8092,7 +8092,7 @@
       <c r="F45" s="21"/>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.15" thickBot="1">
+    <row r="46" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E46" s="39"/>
       <c r="H46" s="40"/>
     </row>
@@ -8103,56 +8103,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="38" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="29" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B46">
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37:E38 D40:E42 E45">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D37)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8204,20 +8204,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:L166"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="9" width="8.75" style="23"/>
-    <col min="10" max="10" width="10.75" style="23" customWidth="1"/>
-    <col min="11" max="16384" width="8.75" style="23"/>
+    <col min="8" max="9" width="8.69921875" style="23"/>
+    <col min="10" max="10" width="10.69921875" style="23" customWidth="1"/>
+    <col min="11" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -8227,7 +8227,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -8241,10 +8241,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:12" ht="25.15">
+    <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>46082</v>
       </c>
@@ -8295,7 +8295,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:12" ht="50.45">
+    <row r="10" spans="1:12" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46083</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46083</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="37.9">
+    <row r="12" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46083</v>
       </c>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="L12" s="64"/>
     </row>
-    <row r="13" spans="1:12" ht="37.9">
+    <row r="13" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46084</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="37.9">
+    <row r="14" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46085</v>
       </c>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="L14" s="64"/>
     </row>
-    <row r="15" spans="1:12" ht="37.9">
+    <row r="15" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46085</v>
       </c>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L15" s="64"/>
     </row>
-    <row r="16" spans="1:12" ht="37.9">
+    <row r="16" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46085</v>
       </c>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="L16" s="64"/>
     </row>
-    <row r="17" spans="1:12" ht="25.15">
+    <row r="17" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46085</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="25.15">
+    <row r="18" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46086</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="50.45">
+    <row r="19" spans="1:12" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46086</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="37.9">
+    <row r="20" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46087</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="25.15">
+    <row r="21" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46087</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="37.9">
+    <row r="22" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46088</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="37.9">
+    <row r="23" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46088</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="25.15">
+    <row r="24" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46088</v>
       </c>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="L24" s="64"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>46088</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>46089</v>
       </c>
@@ -8815,7 +8815,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:12" ht="37.9">
+    <row r="27" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46090</v>
       </c>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="L27" s="64"/>
     </row>
-    <row r="28" spans="1:12" ht="25.15">
+    <row r="28" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46090</v>
       </c>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="L28" s="64"/>
     </row>
-    <row r="29" spans="1:12" ht="25.15">
+    <row r="29" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46090</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="25.15">
+    <row r="30" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46090</v>
       </c>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="L30" s="64"/>
     </row>
-    <row r="31" spans="1:12" ht="25.15">
+    <row r="31" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46090</v>
       </c>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="L31" s="64"/>
     </row>
-    <row r="32" spans="1:12" ht="25.15">
+    <row r="32" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46090</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="25.15">
+    <row r="33" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46090</v>
       </c>
@@ -9036,7 +9036,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="37.9">
+    <row r="34" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46091</v>
       </c>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="L34" s="64"/>
     </row>
-    <row r="35" spans="1:12" ht="37.9">
+    <row r="35" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46091</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="25.15">
+    <row r="36" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46091</v>
       </c>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="L36" s="64"/>
     </row>
-    <row r="37" spans="1:12" ht="25.15">
+    <row r="37" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46091</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="25.15">
+    <row r="38" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46091</v>
       </c>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="L38" s="64"/>
     </row>
-    <row r="39" spans="1:12" ht="25.15">
+    <row r="39" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46091</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>0.74652777777777779</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>46092</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="25.15">
+    <row r="41" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>46092</v>
       </c>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="L41" s="64"/>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="22">
         <v>46092</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="25.15">
+    <row r="43" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>46092</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="25.15">
+    <row r="44" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A44" s="22">
         <v>46092</v>
       </c>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="L44" s="64"/>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="22">
         <v>46092</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>0.6791666666666667</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="25.15">
+    <row r="46" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A46" s="22">
         <v>46092</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>0.71736111111111112</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="25.15">
+    <row r="47" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A47" s="22">
         <v>46093</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="25.15">
+    <row r="48" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A48" s="22">
         <v>46093</v>
       </c>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="L48" s="64"/>
     </row>
-    <row r="49" spans="1:12" ht="25.15">
+    <row r="49" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A49" s="22">
         <v>46093</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="25.15">
+    <row r="50" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A50" s="22">
         <v>46093</v>
       </c>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="L50" s="64"/>
     </row>
-    <row r="51" spans="1:12" ht="25.15">
+    <row r="51" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A51" s="22">
         <v>46093</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="37.9">
+    <row r="52" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A52" s="22">
         <v>46093</v>
       </c>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="L52" s="64"/>
     </row>
-    <row r="53" spans="1:12" ht="25.15">
+    <row r="53" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A53" s="22">
         <v>46093</v>
       </c>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="L53" s="64"/>
     </row>
-    <row r="54" spans="1:12" ht="25.15">
+    <row r="54" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A54" s="22">
         <v>46094</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="22">
         <v>46094</v>
       </c>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="L55" s="64"/>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="22">
         <v>46094</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="25.15">
+    <row r="57" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A57" s="22">
         <v>46094</v>
       </c>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L57" s="64"/>
     </row>
-    <row r="58" spans="1:12" ht="25.15">
+    <row r="58" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A58" s="22">
         <v>46094</v>
       </c>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="L58" s="64"/>
     </row>
-    <row r="59" spans="1:12" ht="25.15">
+    <row r="59" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A59" s="22">
         <v>46094</v>
       </c>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="L59" s="64"/>
     </row>
-    <row r="60" spans="1:12" ht="25.15">
+    <row r="60" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A60" s="22">
         <v>46094</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>0.68958333333333333</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="31">
         <v>46095</v>
       </c>
@@ -9905,7 +9905,7 @@
       <c r="I61" s="35"/>
       <c r="J61" s="35"/>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="31">
         <v>46096</v>
       </c>
@@ -9924,7 +9924,7 @@
       <c r="I62" s="35"/>
       <c r="J62" s="35"/>
     </row>
-    <row r="63" spans="1:12" ht="37.9">
+    <row r="63" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A63" s="22">
         <v>46097</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="25.15">
+    <row r="64" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A64" s="22">
         <v>46097</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
         <v>46097</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>0.43055555555555558</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
         <v>46097</v>
       </c>
@@ -10048,7 +10048,7 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="25.15">
+    <row r="67" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
         <v>46097</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="25.15">
+    <row r="68" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
         <v>46097</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="25.15">
+    <row r="69" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
         <v>46097</v>
       </c>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="L69" s="64"/>
     </row>
-    <row r="70" spans="1:12" ht="25.15">
+    <row r="70" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
         <v>46097</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="25.15">
+    <row r="71" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
         <v>46097</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>0.69027777777777777</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="25.15">
+    <row r="72" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
         <v>46097</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="25.15">
+    <row r="73" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
         <v>46098</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>0.37083333333333335</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="50.45">
+    <row r="74" spans="1:12" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
         <v>46098</v>
       </c>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="L74" s="64"/>
     </row>
-    <row r="75" spans="1:12" ht="25.15">
+    <row r="75" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
         <v>46098</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="25.15">
+    <row r="76" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A76" s="22">
         <v>46098</v>
       </c>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="L76" s="64"/>
     </row>
-    <row r="77" spans="1:12" ht="37.9">
+    <row r="77" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A77" s="22">
         <v>46098</v>
       </c>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="L77" s="64"/>
     </row>
-    <row r="78" spans="1:12" ht="25.15">
+    <row r="78" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A78" s="22">
         <v>46099</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="37.9">
+    <row r="79" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A79" s="22">
         <v>46099</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="25.15">
+    <row r="80" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A80" s="22">
         <v>46099</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>0.48819444444444443</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="25.15">
+    <row r="81" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A81" s="22">
         <v>46099</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>0.49722222222222223</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="37.9">
+    <row r="82" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A82" s="22">
         <v>46099</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="25.15">
+    <row r="83" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A83" s="22">
         <v>46099</v>
       </c>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L83" s="64"/>
     </row>
-    <row r="84" spans="1:12" ht="25.15">
+    <row r="84" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A84" s="22">
         <v>46100</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="22">
         <v>46100</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="25.15">
+    <row r="86" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A86" s="22">
         <v>46100</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="37.9">
+    <row r="87" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A87" s="22">
         <v>46100</v>
       </c>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="L87" s="64"/>
     </row>
-    <row r="88" spans="1:12" ht="25.15">
+    <row r="88" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A88" s="22">
         <v>46100</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>0.58888888888888891</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="37.9">
+    <row r="89" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A89" s="22">
         <v>46100</v>
       </c>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="L89" s="64"/>
     </row>
-    <row r="90" spans="1:12" ht="25.15">
+    <row r="90" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A90" s="22">
         <v>46100</v>
       </c>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="L90" s="64"/>
     </row>
-    <row r="91" spans="1:12" ht="25.15">
+    <row r="91" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A91" s="22">
         <v>46101</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="25.15">
+    <row r="92" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A92" s="22">
         <v>46101</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>0.37152777777777779</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="25.15">
+    <row r="93" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A93" s="22">
         <v>46101</v>
       </c>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L93" s="64"/>
     </row>
-    <row r="94" spans="1:12" ht="25.15">
+    <row r="94" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A94" s="22">
         <v>46101</v>
       </c>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="L94" s="64"/>
     </row>
-    <row r="95" spans="1:12" ht="25.15">
+    <row r="95" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A95" s="22">
         <v>46101</v>
       </c>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="L95" s="64"/>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="22">
         <v>46101</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>0.55069444444444449</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="63">
+    <row r="97" spans="1:12" ht="63" x14ac:dyDescent="0.2">
       <c r="A97" s="22">
         <v>46101</v>
       </c>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L97" s="64"/>
     </row>
-    <row r="98" spans="1:12" ht="25.15">
+    <row r="98" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A98" s="22">
         <v>46101</v>
       </c>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="L98" s="64"/>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="31">
         <v>46102</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="31">
         <v>46103</v>
       </c>
@@ -11103,7 +11103,7 @@
       <c r="I100" s="35"/>
       <c r="J100" s="35"/>
     </row>
-    <row r="101" spans="1:12" ht="50.45">
+    <row r="101" spans="1:12" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A101" s="22">
         <v>46104</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>0.36805555555555558</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="37.9">
+    <row r="102" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A102" s="22">
         <v>46104</v>
       </c>
@@ -11165,7 +11165,7 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="25.15">
+    <row r="103" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A103" s="22">
         <v>46104</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="22">
         <v>46104</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>0.58611111111111114</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="22">
         <v>46104</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>0.60347222222222219</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="50.45">
+    <row r="106" spans="1:12" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A106" s="22">
         <v>46104</v>
       </c>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="L106" s="64"/>
     </row>
-    <row r="107" spans="1:12" ht="37.9">
+    <row r="107" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A107" s="22">
         <v>46104</v>
       </c>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="L107" s="64"/>
     </row>
-    <row r="108" spans="1:12" ht="37.9">
+    <row r="108" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A108" s="22">
         <v>46104</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="25.15">
+    <row r="109" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A109" s="22">
         <v>46105</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>0.39791666666666664</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="22">
         <v>46105</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="22">
         <v>46105</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>0.51388888888888884</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="37.9">
+    <row r="112" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A112" s="22">
         <v>46105</v>
       </c>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="L112" s="64"/>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="22">
         <v>46105</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="25.15">
+    <row r="114" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A114" s="22">
         <v>46105</v>
       </c>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="L114" s="64"/>
     </row>
-    <row r="115" spans="1:12" ht="25.15">
+    <row r="115" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A115" s="22">
         <v>46105</v>
       </c>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="L115" s="64"/>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="22">
         <v>46106</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>0.33958333333333335</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="25.15">
+    <row r="117" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A117" s="22">
         <v>46106</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="25.15">
+    <row r="118" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A118" s="22">
         <v>46106</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>0.49791666666666667</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="22">
         <v>46106</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="25.15">
+    <row r="120" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A120" s="22">
         <v>46106</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="25.15">
+    <row r="121" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A121" s="22">
         <v>46106</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="25.15">
+    <row r="122" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A122" s="22">
         <v>46106</v>
       </c>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="L122" s="64"/>
     </row>
-    <row r="123" spans="1:12" ht="25.15">
+    <row r="123" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A123" s="22">
         <v>46106</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>0.72013888888888888</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="25.15">
+    <row r="124" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A124" s="22">
         <v>46107</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>0.37222222222222223</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="25.15">
+    <row r="125" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A125" s="22">
         <v>46107</v>
       </c>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="L125" s="64"/>
     </row>
-    <row r="126" spans="1:12" ht="37.9">
+    <row r="126" spans="1:12" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A126" s="22">
         <v>46107</v>
       </c>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="L126" s="64"/>
     </row>
-    <row r="127" spans="1:12" ht="25.15">
+    <row r="127" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A127" s="22">
         <v>46107</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="25.15">
+    <row r="128" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A128" s="22">
         <v>46107</v>
       </c>
@@ -11977,7 +11977,7 @@
         <v>0.49166666666666664</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="25.15">
+    <row r="129" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A129" s="22">
         <v>46107</v>
       </c>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="L129" s="64"/>
     </row>
-    <row r="130" spans="1:12" ht="25.15">
+    <row r="130" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A130" s="22">
         <v>46107</v>
       </c>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="L130" s="64"/>
     </row>
-    <row r="131" spans="1:12" ht="25.15">
+    <row r="131" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A131" s="22">
         <v>46107</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>0.6645833333333333</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="25.15">
+    <row r="132" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A132" s="22">
         <v>46107</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="25.15">
+    <row r="133" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A133" s="22">
         <v>46108</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>0.34930555555555554</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="22">
         <v>46108</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>0.40277777777777779</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="25.15">
+    <row r="135" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A135" s="22">
         <v>46108</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>0.43541666666666667</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="25.15">
+    <row r="136" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A136" s="22">
         <v>46108</v>
       </c>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="L136" s="64"/>
     </row>
-    <row r="137" spans="1:12" ht="25.15">
+    <row r="137" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A137" s="22">
         <v>46108</v>
       </c>
@@ -12242,7 +12242,9 @@
       <c r="E137" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F137" s="27"/>
+      <c r="F137" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="G137" s="28" t="s">
         <v>135</v>
       </c>
@@ -12258,7 +12260,7 @@
       </c>
       <c r="L137" s="64"/>
     </row>
-    <row r="138" spans="1:12" ht="25.15">
+    <row r="138" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A138" s="22">
         <v>46108</v>
       </c>
@@ -12289,7 +12291,7 @@
         <v>0.52569444444444446</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="25.15">
+    <row r="139" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A139" s="22">
         <v>46108</v>
       </c>
@@ -12320,7 +12322,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="25.15">
+    <row r="140" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A140" s="22">
         <v>46108</v>
       </c>
@@ -12352,7 +12354,7 @@
       </c>
       <c r="L140" s="64"/>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="31">
         <v>46109</v>
       </c>
@@ -12371,7 +12373,7 @@
       <c r="I141" s="35"/>
       <c r="J141" s="35"/>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="31">
         <v>46110</v>
       </c>
@@ -12390,7 +12392,7 @@
       <c r="I142" s="35"/>
       <c r="J142" s="35"/>
     </row>
-    <row r="143" spans="1:12" ht="25.15">
+    <row r="143" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A143" s="22">
         <v>46111</v>
       </c>
@@ -12421,7 +12423,7 @@
         <v>0.34930555555555554</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="25.15">
+    <row r="144" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A144" s="22">
         <v>46111</v>
       </c>
@@ -12452,7 +12454,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="25.15">
+    <row r="145" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A145" s="22">
         <v>46111</v>
       </c>
@@ -12484,7 +12486,7 @@
       </c>
       <c r="L145" s="64"/>
     </row>
-    <row r="146" spans="1:12" ht="25.15">
+    <row r="146" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A146" s="22">
         <v>46111</v>
       </c>
@@ -12515,7 +12517,7 @@
         <v>0.50347222222222221</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="25.15">
+    <row r="147" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A147" s="22">
         <v>46111</v>
       </c>
@@ -12546,7 +12548,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="25.15">
+    <row r="148" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A148" s="22">
         <v>46111</v>
       </c>
@@ -12577,7 +12579,7 @@
         <v>0.68472222222222223</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="25.15">
+    <row r="149" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A149" s="22">
         <v>46111</v>
       </c>
@@ -12608,7 +12610,7 @@
         <v>0.73263888888888884</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="25.15">
+    <row r="150" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A150" s="22">
         <v>46112</v>
       </c>
@@ -12640,7 +12642,7 @@
       </c>
       <c r="L150" s="64"/>
     </row>
-    <row r="151" spans="1:12" ht="25.15">
+    <row r="151" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A151" s="22">
         <v>46112</v>
       </c>
@@ -12671,7 +12673,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="25.15">
+    <row r="152" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A152" s="22">
         <v>46112</v>
       </c>
@@ -12702,7 +12704,7 @@
         <v>0.48680555555555555</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="25.15">
+    <row r="153" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A153" s="22">
         <v>46112</v>
       </c>
@@ -12734,7 +12736,7 @@
       </c>
       <c r="L153" s="64"/>
     </row>
-    <row r="154" spans="1:12" ht="25.15">
+    <row r="154" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A154" s="22">
         <v>46112</v>
       </c>
@@ -12766,7 +12768,7 @@
       </c>
       <c r="L154" s="64"/>
     </row>
-    <row r="155" spans="1:12" ht="25.15">
+    <row r="155" spans="1:12" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A155" s="22">
         <v>46112</v>
       </c>
@@ -12797,7 +12799,7 @@
         <v>0.71180555555555558</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="13.9" customHeight="1">
+    <row r="156" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="22">
         <v>46112</v>
       </c>
@@ -12828,7 +12830,7 @@
         <v>0.73611111111111116</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="13.9" customHeight="1" thickBot="1">
+    <row r="157" spans="1:12" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="46"/>
       <c r="B157" s="46"/>
       <c r="C157" s="45"/>
@@ -12839,7 +12841,7 @@
       <c r="H157" s="36"/>
       <c r="I157" s="37"/>
     </row>
-    <row r="158" spans="1:12" ht="13.9" customHeight="1">
+    <row r="158" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="5"/>
@@ -12853,7 +12855,7 @@
       </c>
       <c r="H158" s="40"/>
     </row>
-    <row r="159" spans="1:12" ht="13.9" customHeight="1" thickBot="1">
+    <row r="159" spans="1:12" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="9"/>
@@ -12866,7 +12868,7 @@
       </c>
       <c r="H159" s="40"/>
     </row>
-    <row r="160" spans="1:12" ht="13.9" customHeight="1" thickBot="1">
+    <row r="160" spans="1:12" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="117" t="s">
         <v>27</v>
       </c>
@@ -12877,7 +12879,7 @@
       <c r="F160" s="2"/>
       <c r="H160" s="40"/>
     </row>
-    <row r="161" spans="1:8" ht="13.9">
+    <row r="161" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="13"/>
       <c r="B161" s="13"/>
       <c r="C161" s="6"/>
@@ -12891,7 +12893,7 @@
       </c>
       <c r="H161" s="38"/>
     </row>
-    <row r="162" spans="1:8" ht="15" customHeight="1" thickBot="1">
+    <row r="162" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="118" t="s">
         <v>29</v>
       </c>
@@ -12903,11 +12905,11 @@
       </c>
       <c r="F162" s="18">
         <f>SUMIF(F9:F156,"Non-Billable",H9:H156)</f>
-        <v>7.9354166666666641</v>
+        <v>7.9666666666666641</v>
       </c>
       <c r="H162" s="40"/>
     </row>
-    <row r="163" spans="1:8" ht="14.45" thickBot="1">
+    <row r="163" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -12917,11 +12919,11 @@
       </c>
       <c r="F163" s="44">
         <f>F161+F162</f>
-        <v>7.9354166666666641</v>
+        <v>7.9666666666666641</v>
       </c>
       <c r="H163" s="40"/>
     </row>
-    <row r="164" spans="1:8" ht="13.9" thickBot="1">
+    <row r="164" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -12930,7 +12932,7 @@
       <c r="F164" s="2"/>
       <c r="H164" s="40"/>
     </row>
-    <row r="165" spans="1:8" ht="13.9" thickBot="1">
+    <row r="165" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -12941,7 +12943,7 @@
       <c r="F165" s="21"/>
       <c r="H165" s="40"/>
     </row>
-    <row r="166" spans="1:8" ht="13.15" thickBot="1">
+    <row r="166" spans="1:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E166" s="39"/>
       <c r="H166" s="40"/>
     </row>
@@ -12952,56 +12954,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7 D157:E158">
-    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B166">
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D160:E162 E165">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D160)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13053,18 +13055,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E8809-782A-4EC8-A7EE-23E6EB29126F}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="23"/>
-    <col min="5" max="5" width="13.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="23"/>
+    <col min="5" max="5" width="13.19921875" style="23" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="23"/>
+    <col min="7" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="81"/>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -13072,7 +13074,7 @@
       <c r="E1" s="81"/>
       <c r="F1" s="81"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="80"/>
       <c r="B2" s="80"/>
       <c r="C2" s="85"/>
@@ -13080,7 +13082,7 @@
       <c r="E2" s="85"/>
       <c r="F2" s="85"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="86"/>
@@ -13088,7 +13090,7 @@
       <c r="E3" s="86"/>
       <c r="F3" s="86"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="87"/>
@@ -13096,7 +13098,7 @@
       <c r="E4" s="87"/>
       <c r="F4" s="87"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -13108,7 +13110,7 @@
       <c r="E5" s="87"/>
       <c r="F5" s="87"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="80" t="s">
         <v>140</v>
       </c>
@@ -13121,7 +13123,7 @@
       <c r="E6" s="86"/>
       <c r="F6" s="86"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1">
+    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -13129,125 +13131,125 @@
       <c r="E7" s="86"/>
       <c r="F7" s="86"/>
     </row>
-    <row r="8" spans="1:15" ht="27.4" customHeight="1">
-      <c r="A8" s="124" t="s">
+    <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="130" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="121" t="s">
+      <c r="C9" s="131"/>
+      <c r="D9" s="130" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="122"/>
+      <c r="E9" s="131"/>
       <c r="F9" s="84" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="79"/>
-      <c r="B10" s="123" t="s">
+      <c r="B10" s="121" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123" t="s">
+      <c r="C10" s="121"/>
+      <c r="D10" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="E10" s="123"/>
+      <c r="E10" s="121"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="119" t="s">
+      <c r="G10" s="128" t="s">
         <v>148</v>
       </c>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
-      <c r="B11" s="125" t="s">
+      <c r="B11" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="126"/>
-      <c r="D11" s="123" t="s">
+      <c r="C11" s="120"/>
+      <c r="D11" s="121" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="123"/>
+      <c r="E11" s="121"/>
       <c r="F11" s="78"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
-      <c r="B12" s="125" t="s">
+      <c r="B12" s="119" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
       <c r="F12" s="78"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="79"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
       <c r="F13" s="78"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
-      <c r="B14" s="125"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
       <c r="F14" s="78"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
       <c r="F15" s="78"/>
     </row>
-    <row r="16" spans="1:15" ht="13.15" thickBot="1">
+    <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
-      <c r="B16" s="125"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="121"/>
       <c r="F16" s="78"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="127" t="s">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="122" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="129"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="124"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="74"/>
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
@@ -13257,6 +13259,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -13266,16 +13278,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13305,19 +13307,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517D5F3-AC91-43ED-96BB-0299CBED5EE0}">
   <dimension ref="A4:F23"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.75" style="23"/>
+    <col min="2" max="2" width="11.69921875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="132"/>
       <c r="B4" s="132"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -13325,23 +13327,23 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="80" t="s">
         <v>153</v>
       </c>
       <c r="B6" s="80"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="96" t="s">
         <v>154</v>
       </c>
       <c r="B7" s="96"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="97"/>
       <c r="B8" s="86"/>
     </row>
-    <row r="9" spans="1:6" ht="27.4" customHeight="1">
+    <row r="9" spans="1:6" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="145" t="s">
         <v>155</v>
       </c>
@@ -13351,7 +13353,7 @@
       <c r="E9" s="145"/>
       <c r="F9" s="145"/>
     </row>
-    <row r="10" spans="1:6" ht="25.15">
+    <row r="10" spans="1:6" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A10" s="88" t="s">
         <v>156</v>
       </c>
@@ -13371,7 +13373,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="88"/>
       <c r="B11" s="88"/>
       <c r="C11" s="88"/>
@@ -13379,7 +13381,7 @@
       <c r="E11" s="88"/>
       <c r="F11" s="88"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="88"/>
       <c r="B12" s="88"/>
       <c r="C12" s="88"/>
@@ -13387,7 +13389,7 @@
       <c r="E12" s="88"/>
       <c r="F12" s="88"/>
     </row>
-    <row r="13" spans="1:6" ht="13.15" thickBot="1">
+    <row r="13" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="88"/>
       <c r="B13" s="88"/>
       <c r="C13" s="88"/>
@@ -13395,7 +13397,7 @@
       <c r="E13" s="88"/>
       <c r="F13" s="88"/>
     </row>
-    <row r="14" spans="1:6" ht="13.15" thickBot="1">
+    <row r="14" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="89"/>
       <c r="B14" s="90"/>
       <c r="C14" s="90"/>
@@ -13406,7 +13408,7 @@
       <c r="E14" s="90"/>
       <c r="F14" s="92"/>
     </row>
-    <row r="15" spans="1:6" ht="13.15" thickBot="1">
+    <row r="15" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="136"/>
       <c r="B15" s="137"/>
       <c r="C15" s="137"/>
@@ -13414,7 +13416,7 @@
       <c r="E15" s="137"/>
       <c r="F15" s="137"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="146" t="s">
         <v>162</v>
       </c>
@@ -13424,7 +13426,7 @@
       <c r="E16" s="147"/>
       <c r="F16" s="148"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="133"/>
       <c r="B17" s="134"/>
       <c r="C17" s="134"/>
@@ -13432,7 +13434,7 @@
       <c r="E17" s="134"/>
       <c r="F17" s="135"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="133"/>
       <c r="B18" s="134"/>
       <c r="C18" s="134"/>
@@ -13440,7 +13442,7 @@
       <c r="E18" s="134"/>
       <c r="F18" s="135"/>
     </row>
-    <row r="19" spans="1:6" ht="13.15" thickBot="1">
+    <row r="19" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="136"/>
       <c r="B19" s="137"/>
       <c r="C19" s="137"/>
@@ -13448,8 +13450,8 @@
       <c r="E19" s="137"/>
       <c r="F19" s="138"/>
     </row>
-    <row r="20" spans="1:6" ht="13.15" thickBot="1"/>
-    <row r="21" spans="1:6">
+    <row r="20" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="93" t="s">
         <v>3</v>
       </c>
@@ -13459,7 +13461,7 @@
       <c r="E21" s="139"/>
       <c r="F21" s="140"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="94" t="s">
         <v>163</v>
       </c>
@@ -13469,7 +13471,7 @@
       <c r="E22" s="141"/>
       <c r="F22" s="142"/>
     </row>
-    <row r="23" spans="1:6" ht="13.15" thickBot="1">
+    <row r="23" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="95" t="s">
         <v>164</v>
       </c>
@@ -13533,18 +13535,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J78"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="52"/>
+    <col min="1" max="1" width="8.69921875" style="52"/>
     <col min="2" max="2" width="25.5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="52"/>
-    <col min="4" max="4" width="19.25" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.75" style="52"/>
-    <col min="6" max="6" width="21.75" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="52"/>
+    <col min="3" max="3" width="8.69921875" style="52"/>
+    <col min="4" max="4" width="19.19921875" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" style="52"/>
+    <col min="6" max="6" width="21.69921875" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="8.69921875" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1">
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="66" t="s">
         <v>33</v>
       </c>
@@ -13561,7 +13563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="66" t="s">
         <v>167</v>
       </c>
@@ -13578,7 +13580,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="66" t="s">
         <v>170</v>
       </c>
@@ -13595,7 +13597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="66" t="s">
         <v>173</v>
       </c>
@@ -13609,7 +13611,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="66" t="s">
         <v>177</v>
       </c>
@@ -13623,7 +13625,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="66" t="s">
         <v>181</v>
       </c>
@@ -13637,7 +13639,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="66" t="s">
         <v>185</v>
       </c>
@@ -13654,7 +13656,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="66" t="s">
         <v>190</v>
       </c>
@@ -13671,7 +13673,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="66" t="s">
         <v>194</v>
       </c>
@@ -13685,7 +13687,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="66" t="s">
         <v>198</v>
       </c>
@@ -13702,7 +13704,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="66" t="s">
         <v>203</v>
       </c>
@@ -13716,7 +13718,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="66" t="s">
         <v>207</v>
       </c>
@@ -13727,7 +13729,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="66" t="s">
         <v>210</v>
       </c>
@@ -13739,7 +13741,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="66" t="s">
         <v>213</v>
       </c>
@@ -13751,7 +13753,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="66" t="s">
         <v>216</v>
       </c>
@@ -13763,7 +13765,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="27.6">
+    <row r="17" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B17" s="66" t="s">
         <v>219</v>
       </c>
@@ -13775,7 +13777,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="66" t="s">
         <v>222</v>
       </c>
@@ -13787,7 +13789,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="66" t="s">
         <v>225</v>
       </c>
@@ -13799,7 +13801,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="66" t="s">
         <v>227</v>
       </c>
@@ -13811,7 +13813,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="66" t="s">
         <v>230</v>
       </c>
@@ -13823,7 +13825,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="66" t="s">
         <v>233</v>
       </c>
@@ -13835,7 +13837,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="66" t="s">
         <v>236</v>
       </c>
@@ -13847,7 +13849,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="66" t="s">
         <v>239</v>
       </c>
@@ -13859,7 +13861,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="66" t="s">
         <v>241</v>
       </c>
@@ -13871,7 +13873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="66" t="s">
         <v>243</v>
       </c>
@@ -13882,7 +13884,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="66" t="s">
         <v>246</v>
       </c>
@@ -13894,7 +13896,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="66" t="s">
         <v>249</v>
       </c>
@@ -13906,7 +13908,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="66" t="s">
         <v>252</v>
       </c>
@@ -13917,7 +13919,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="66" t="s">
         <v>255</v>
       </c>
@@ -13928,7 +13930,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="66" t="s">
         <v>258</v>
       </c>
@@ -13939,7 +13941,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="66" t="s">
         <v>261</v>
       </c>
@@ -13950,7 +13952,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="66" t="s">
         <v>264</v>
       </c>
@@ -13961,7 +13963,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="66" t="s">
         <v>267</v>
       </c>
@@ -13972,7 +13974,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="66" t="s">
         <v>270</v>
       </c>
@@ -13983,7 +13985,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="66" t="s">
         <v>273</v>
       </c>
@@ -13994,7 +13996,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="66" t="s">
         <v>276</v>
       </c>
@@ -14005,7 +14007,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="66" t="s">
         <v>279</v>
       </c>
@@ -14016,7 +14018,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="52" t="s">
         <v>281</v>
       </c>
@@ -14027,7 +14029,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="66" t="s">
         <v>284</v>
       </c>
@@ -14038,7 +14040,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="66" t="s">
         <v>287</v>
       </c>
@@ -14050,7 +14052,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="66" t="s">
         <v>290</v>
       </c>
@@ -14058,7 +14060,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="52" t="s">
         <v>14</v>
       </c>
@@ -14066,179 +14068,179 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="27.6">
+    <row r="44" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B44" s="62"/>
       <c r="H44" s="108" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H45" s="69" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H46" s="112" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="62"/>
       <c r="H47" s="111" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H48" s="113" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="49" spans="8:8">
+    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H49" s="99" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="50" spans="8:8">
+    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H50" s="106" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="51" spans="8:8">
+    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H51" s="110" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="8:8">
+    <row r="52" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H52" s="70" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="53" spans="8:8">
+    <row r="53" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H53" s="70" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="8:8">
+    <row r="54" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H54" s="111" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="55" spans="8:8">
+    <row r="55" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H55" s="70" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="56" spans="8:8">
+    <row r="56" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H56" s="111" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="57" spans="8:8">
+    <row r="57" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H57" s="70" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="58" spans="8:8">
+    <row r="58" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H58" s="111" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="59" spans="8:8">
+    <row r="59" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H59" s="69" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="60" spans="8:8">
+    <row r="60" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H60" s="111" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="61" spans="8:8">
+    <row r="61" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H61" s="69" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="62" spans="8:8">
+    <row r="62" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H62" s="110" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="63" spans="8:8">
+    <row r="63" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H63" s="108" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="8:8">
+    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H64" s="70" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" s="111" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" s="110" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" s="108" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" s="70" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" s="70" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" s="111" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" s="114" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" s="69" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" s="109" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" s="69" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" s="109" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" s="70" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="8:8">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H77" s="71" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="78" spans="8:8">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H78" s="71" t="s">
         <v>40</v>
       </c>
@@ -14259,6 +14261,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -14396,12 +14404,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -14412,15 +14414,38 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9F11A3-1B07-4AC4-B045-F4E913DDCE54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D3CB3FE-59EE-40A7-9368-5A018C1C12CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D3CB3FE-59EE-40A7-9368-5A018C1C12CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9F11A3-1B07-4AC4-B045-F4E913DDCE54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C4E97C2-C664-446D-B13B-4F0AE5EE0AA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C4E97C2-C664-446D-B13B-4F0AE5EE0AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
